--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104494_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104494_W4.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.531</v>
+        <v>8.8406</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2776</v>
+        <v>4.5879</v>
       </c>
       <c r="F2" t="n">
-        <v>5.2533</v>
+        <v>4.2527</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8498</v>
+        <v>3.8632</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6578</v>
+        <v>3.6617</v>
       </c>
       <c r="I2" t="n">
-        <v>0.192</v>
+        <v>0.2015</v>
       </c>
       <c r="J2" t="n">
-        <v>1.8365</v>
+        <v>1.8214</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7246</v>
+        <v>1.7097</v>
       </c>
       <c r="L2" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M2" t="n">
-        <v>2.0133</v>
+        <v>2.0418</v>
       </c>
       <c r="N2" t="n">
-        <v>1.9333</v>
+        <v>1.952</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>3.352</v>
+        <v>0.6681</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3803</v>
+        <v>0.7336</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9717</v>
+        <v>-0.0654</v>
       </c>
       <c r="V2" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="W2" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.364</v>
+        <v>5.161</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7359</v>
+        <v>1.4456</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3719</v>
+        <v>3.7155</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3778</v>
+        <v>1.0434</v>
       </c>
       <c r="H3" t="n">
-        <v>1.9886</v>
+        <v>3.248</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3892</v>
+        <v>-2.2046</v>
       </c>
       <c r="J3" t="n">
-        <v>3.0562</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9816</v>
+        <v>1.4684</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0746</v>
+        <v>-2.2945</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6785</v>
+        <v>1.8694</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.993</v>
+        <v>1.7796</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3145</v>
+        <v>0.0898</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>5.8009</v>
+        <v>-0.7442</v>
       </c>
       <c r="T3" t="n">
-        <v>6.0822</v>
+        <v>0.1414</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2813</v>
+        <v>-0.8855</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5463</v>
+        <v>3.2684</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.2684</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.0142</v>
+        <v>3.3499</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3627</v>
+        <v>1.1607</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6514</v>
+        <v>2.1892</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0378</v>
+        <v>3.702</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2422</v>
+        <v>1.1083</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.2044</v>
+        <v>2.5937</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.8023</v>
+        <v>1.9905</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4821</v>
+        <v>-0.3555</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.2844</v>
+        <v>2.3459</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8401</v>
+        <v>1.7115</v>
       </c>
       <c r="N4" t="n">
-        <v>1.7601</v>
+        <v>1.4638</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08</v>
+        <v>0.2477</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>2.2763</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8895</v>
+        <v>-0.5585</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0212</v>
+        <v>0.1506</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9107</v>
+        <v>-0.7091</v>
       </c>
       <c r="V4" t="n">
-        <v>3.278</v>
+        <v>-0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>3.278</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5238</v>
+        <v>2.7359</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3215</v>
+        <v>1.3983</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2023</v>
+        <v>1.3376</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1153</v>
+        <v>4.1106</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3246</v>
+        <v>1.3268</v>
       </c>
       <c r="I5" t="n">
-        <v>2.7908</v>
+        <v>2.7838</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7274</v>
+        <v>3.6926</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2326</v>
+        <v>1.2131</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4948</v>
+        <v>2.4795</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3879</v>
+        <v>0.4179</v>
       </c>
       <c r="N5" t="n">
-        <v>0.092</v>
+        <v>0.1137</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7238</v>
+        <v>-0.5144</v>
       </c>
       <c r="T5" t="n">
-        <v>0.248</v>
+        <v>0.369</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9718</v>
+        <v>-0.8834</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.8678</v>
+        <v>-0.8603</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1045</v>
+        <v>1.6989</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3568</v>
+        <v>2.0502</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7476</v>
+        <v>-0.3513</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6906</v>
+        <v>2.367</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1023</v>
+        <v>1.9766</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5883</v>
+        <v>0.3903</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0077</v>
+        <v>3.0285</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3432</v>
+        <v>2.954</v>
       </c>
       <c r="L6" t="n">
-        <v>2.351</v>
+        <v>0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>1.6829</v>
+        <v>-0.6615</v>
       </c>
       <c r="N6" t="n">
-        <v>1.4455</v>
+        <v>-0.9774</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2373</v>
+        <v>0.3159</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7884</v>
+        <v>2.153</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6775</v>
+        <v>2.4362</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1109</v>
+        <v>-0.2832</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9012</v>
+        <v>1.475</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4402</v>
+        <v>0.6093</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3413</v>
+        <v>0.8657</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3852</v>
+        <v>0.3949</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6885</v>
+        <v>-1.6724</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0737</v>
+        <v>2.0673</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9418</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6478</v>
+        <v>-0.6516999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5689</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0407</v>
+        <v>-1.0207</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S7" t="n">
-        <v>0.516</v>
+        <v>1.0802</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2601</v>
+        <v>0.8057</v>
       </c>
       <c r="U7" t="n">
-        <v>0.776</v>
+        <v>0.2744</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>T. MALEDON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0141</v>
+        <v>0.4116</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1413</v>
+        <v>-1.1566</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1272</v>
+        <v>1.5682</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4302</v>
+        <v>-1.6392</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7821</v>
+        <v>-1.6687</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3519</v>
+        <v>0.0296</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1776</v>
+        <v>-2.3569</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.2149</v>
+        <v>-1.9692</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>-0.3877</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2526</v>
+        <v>0.7178</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5672</v>
+        <v>0.3005</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3145</v>
+        <v>0.4173</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0375</v>
+        <v>0.7839</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0363</v>
+        <v>0.9822</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0738</v>
+        <v>-0.1983</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.9497</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.4945</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. MALEDON</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5706</v>
+        <v>0.2338</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7036</v>
+        <v>-0.0281</v>
       </c>
       <c r="F9" t="n">
-        <v>1.133</v>
+        <v>0.2619</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6349</v>
+        <v>-0.4282</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6695</v>
+        <v>-0.7813</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0346</v>
+        <v>0.3531</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.3292</v>
+        <v>-0.1836</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9506</v>
+        <v>-0.2208</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3786</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>0.6943</v>
+        <v>-0.2446</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2811</v>
+        <v>-0.5604</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4132</v>
+        <v>0.3159</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2156</v>
+        <v>0.2067</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3871</v>
+        <v>0.1555</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6028</v>
+        <v>0.0512</v>
       </c>
       <c r="V9" t="n">
-        <v>1.9604</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.5068</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8605</v>
+        <v>-0.125</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.499</v>
+        <v>-1.0343</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6385</v>
+        <v>0.9093</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1249</v>
+        <v>0.1397</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2643</v>
+        <v>-0.2506</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3892</v>
+        <v>0.3903</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3134</v>
+        <v>-0.3187</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3983</v>
+        <v>0.3964</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4383</v>
+        <v>0.4584</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1009</v>
+        <v>1.1055</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7585</v>
+        <v>-0.037</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0514</v>
+        <v>0.4226</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7071</v>
+        <v>-0.4596</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7405</v>
+        <v>-2.0249</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.104</v>
+        <v>-2.4052</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3635</v>
+        <v>0.3803</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7405</v>
+        <v>-0.7356</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0924</v>
+        <v>-1.0887</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3519</v>
+        <v>0.3531</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6451</v>
+        <v>-0.649</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0</v>
+        <v>0.7107</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1905</v>
+        <v>0.5201</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1905</v>
+        <v>0.1906</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.6904</v>
+        <v>-3.467</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6173</v>
+        <v>-5.4275</v>
       </c>
       <c r="F12" t="n">
-        <v>1.927</v>
+        <v>1.9605</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.1124</v>
+        <v>-2.1129</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2755</v>
+        <v>1.2807</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3879</v>
+        <v>-3.3936</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.3004</v>
+        <v>-2.3309</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6958</v>
+        <v>0.6787</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.9962</v>
+        <v>-3.0096</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1879</v>
+        <v>0.2179</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5797</v>
+        <v>0.6019</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4023</v>
+        <v>-0.1672</v>
       </c>
       <c r="T12" t="n">
-        <v>0.127</v>
+        <v>0.3665</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5293</v>
+        <v>-0.5337</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.9086</v>
+        <v>-3.6251</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7569</v>
+        <v>-2.7176</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1518</v>
+        <v>-0.9075</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.6109</v>
+        <v>-2.6042</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7735</v>
+        <v>-2.7635</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1626</v>
+        <v>0.1592</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.3725</v>
+        <v>-2.3876</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.2205</v>
+        <v>-2.231</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.152</v>
+        <v>-0.1566</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2384</v>
+        <v>-0.2166</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.553</v>
+        <v>-0.5325</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9367</v>
+        <v>0.345</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2087</v>
+        <v>0.8569</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.728</v>
+        <v>-0.5119</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.654</v>
+        <v>14.6647</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.207800000000001</v>
+        <v>-1.517299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>15.8614</v>
+        <v>16.1821</v>
       </c>
       <c r="G14" t="n">
-        <v>8.052499999999998</v>
+        <v>8.1007</v>
       </c>
       <c r="H14" t="n">
-        <v>4.320700000000002</v>
+        <v>4.376899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>3.731899999999998</v>
+        <v>3.7237</v>
       </c>
       <c r="J14" t="n">
-        <v>2.641399999999999</v>
+        <v>2.422</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4555</v>
+        <v>2.3059</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1860000000000005</v>
+        <v>0.1159</v>
       </c>
       <c r="M14" t="n">
-        <v>5.4109</v>
+        <v>5.678500000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8653</v>
+        <v>2.0709</v>
       </c>
       <c r="O14" t="n">
-        <v>3.5453</v>
+        <v>3.607800000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.670699999999999</v>
+        <v>-5.6907</v>
       </c>
       <c r="Q14" t="n">
-        <v>-24.9517</v>
+        <v>-25.0396</v>
       </c>
       <c r="R14" t="n">
-        <v>19.2807</v>
+        <v>19.3487</v>
       </c>
       <c r="S14" t="n">
-        <v>3.916600000000001</v>
+        <v>3.9263</v>
       </c>
       <c r="T14" t="n">
-        <v>7.8939</v>
+        <v>7.940300000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.9775</v>
+        <v>-4.0139</v>
       </c>
       <c r="V14" t="n">
-        <v>8.355599999999999</v>
+        <v>8.328799999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>13.2086</v>
+        <v>13.1601</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.8529</v>
+        <v>-4.8312</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2908</v>
+        <v>4.1246</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9092</v>
+        <v>1.65</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3816</v>
+        <v>2.4746</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0851</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1255</v>
+        <v>-0.129</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2106</v>
+        <v>0.2131</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0091</v>
+        <v>-0.0337</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4542</v>
+        <v>-0.4729</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M15" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.1178</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3288</v>
+        <v>0.3438</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8447</v>
+        <v>0.6747</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2794</v>
+        <v>1.0494</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4346</v>
+        <v>-0.3747</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1341</v>
+        <v>2.6424</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7507</v>
+        <v>0.9159</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3834</v>
+        <v>1.7264</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3693</v>
+        <v>1.3844</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5669</v>
+        <v>0.5767</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8024</v>
+        <v>0.8076</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5178</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4431</v>
+        <v>0.4342</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8515</v>
+        <v>0.8757</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1238</v>
+        <v>0.1426</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7277</v>
+        <v>0.7331</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4355</v>
+        <v>-0.95</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9134</v>
+        <v>0.0902</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.3489</v>
+        <v>-1.0402</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. GOLDEN</t>
+          <t>H. BENITEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9361</v>
+        <v>1.3782</v>
       </c>
       <c r="E17" t="n">
-        <v>4.0847</v>
+        <v>1.3055</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1486</v>
+        <v>0.0728</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2995</v>
+        <v>2.1042</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7739</v>
+        <v>3.2778</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4744</v>
+        <v>-1.1736</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6366</v>
+        <v>2.3023</v>
       </c>
       <c r="K17" t="n">
-        <v>2.562</v>
+        <v>3.0919</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>-0.7896</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3371</v>
+        <v>-0.1981</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.788</v>
+        <v>0.1859</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.549</v>
+        <v>-0.384</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.4952</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>2.9488</v>
+        <v>2.2763</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6612</v>
+        <v>-0.547</v>
       </c>
       <c r="T17" t="n">
-        <v>3.2362</v>
+        <v>0.369</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.575</v>
+        <v>-0.916</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4783</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. BENITEZ</t>
+          <t>G. GOLDEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3848</v>
+        <v>1.297</v>
       </c>
       <c r="E18" t="n">
-        <v>0.749</v>
+        <v>2.3816</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3642</v>
+        <v>-1.0845</v>
       </c>
       <c r="G18" t="n">
-        <v>2.1135</v>
+        <v>1.2721</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2916</v>
+        <v>1.7395</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1781</v>
+        <v>-0.4674</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3338</v>
+        <v>2.5901</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1201</v>
+        <v>2.5156</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7864</v>
+        <v>0.0745</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2203</v>
+        <v>-1.318</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1715</v>
+        <v>-0.7761</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3918</v>
+        <v>-0.5419</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2683</v>
+        <v>2.9592</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5434</v>
+        <v>1.0462</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2238</v>
+        <v>1.5929</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3196</v>
+        <v>-0.5468</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>-1.4764</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. IZAW-BOLAVIE</t>
+          <t>A. UBAL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0013</v>
+        <v>0.3856</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2087</v>
+        <v>-0.0217</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2099</v>
+        <v>0.4073</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6313</v>
+        <v>-0.1718</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4154</v>
+        <v>-0.376</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2159</v>
+        <v>0.2041</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.5727</v>
+        <v>0.6567</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5727</v>
+        <v>-0.3038</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.9605</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0586</v>
+        <v>-0.8285</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1573</v>
+        <v>-0.0722</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2159</v>
+        <v>-0.7563</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>2.5039</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4058</v>
+        <v>0.3297</v>
       </c>
       <c r="T19" t="n">
-        <v>1.364</v>
+        <v>0.5084</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0417</v>
+        <v>-0.1786</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,19 +1969,19 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -1996,10 +1996,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. UBAL</t>
+          <t>A. IZAW-BOLAVIE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4228</v>
+        <v>-0.881</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5841</v>
+        <v>-1.1567</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1613</v>
+        <v>0.2757</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1682</v>
+        <v>-1.6358</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3708</v>
+        <v>-1.4214</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2026</v>
+        <v>-0.2144</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6763</v>
+        <v>-1.5793</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2913</v>
+        <v>-1.5793</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9675</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8444</v>
+        <v>-0.0565</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0795</v>
+        <v>0.1579</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7649</v>
+        <v>-0.2144</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.4952</v>
+        <v>0.2276</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4815</v>
+        <v>0.5272</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0847</v>
+        <v>0.4226</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3968</v>
+        <v>0.1046</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5072</v>
+        <v>-2.7807</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5601</v>
+        <v>-2.6621</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0529</v>
+        <v>-0.1186</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.0403</v>
+        <v>-3.0545</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.583</v>
+        <v>-2.5923</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.3624</v>
+        <v>-2.4106</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3006</v>
+        <v>0.2716</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.663</v>
+        <v>-2.6822</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.6439</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7579</v>
+        <v>-0.7337</v>
       </c>
       <c r="O22" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P22" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R22" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4572</v>
+        <v>-0.7341</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.744</v>
+        <v>0.2037</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.9378</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.7142</v>
+        <v>-3.344</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5786</v>
+        <v>-2.2325</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1357</v>
+        <v>-1.1116</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4446</v>
+        <v>0.4596</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0059</v>
+        <v>0.0051</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4505</v>
+        <v>0.4545</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1585</v>
+        <v>0.1579</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M23" t="n">
-        <v>0.286</v>
+        <v>0.3018</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.293</v>
+        <v>-0.9418</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8242</v>
+        <v>-0.8278</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2011</v>
+        <v>-4.4429</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.4881</v>
+        <v>-6.8297</v>
       </c>
       <c r="F24" t="n">
-        <v>2.287</v>
+        <v>2.3867</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7805</v>
+        <v>-1.7917</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.3345</v>
+        <v>-3.3454</v>
       </c>
       <c r="I24" t="n">
-        <v>1.554</v>
+        <v>1.5537</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9443</v>
+        <v>-1.9792</v>
       </c>
       <c r="K24" t="n">
-        <v>-2.9865</v>
+        <v>-3.0142</v>
       </c>
       <c r="L24" t="n">
-        <v>1.0422</v>
+        <v>1.035</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1638</v>
+        <v>0.1875</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O24" t="n">
-        <v>0.5118</v>
+        <v>0.5187</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.7635</v>
+        <v>-4.7803</v>
       </c>
       <c r="R24" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0576</v>
+        <v>-0.287</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7803</v>
+        <v>-0.0702</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2774</v>
+        <v>-0.2168</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.0308</v>
+        <v>-5.5702</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.036</v>
+        <v>-2.6916</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9948</v>
+        <v>-2.8786</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.3466</v>
+        <v>-2.3445</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.443</v>
+        <v>-1.4418</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.9036</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.5208</v>
+        <v>-1.5276</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.7379</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.8258</v>
+        <v>-0.8169</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7086</v>
+        <v>-0.7039</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P25" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.633</v>
+        <v>-0.1849</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3811</v>
+        <v>-0.0258</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2519</v>
+        <v>-0.159</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.3518</v>
+        <v>-5.7222</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.8997</v>
+        <v>-6.8408</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5479000000000001</v>
+        <v>1.1186</v>
       </c>
       <c r="G26" t="n">
-        <v>-4.2243</v>
+        <v>-4.2342</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.6276</v>
+        <v>-2.6279</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.5967</v>
+        <v>-1.6062</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.3246</v>
+        <v>-4.3639</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.3733</v>
+        <v>-2.3969</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.9513</v>
+        <v>-1.967</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1002</v>
+        <v>0.1297</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2543</v>
+        <v>-0.231</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P26" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R26" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.9272</v>
+        <v>-1.28</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1331</v>
+        <v>-0.0122</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.7941</v>
+        <v>-1.2678</v>
       </c>
       <c r="V26" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4141</v>
+        <v>1.405</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-14.654</v>
+        <v>-13.0856</v>
       </c>
       <c r="E27" t="n">
-        <v>-15.8617</v>
+        <v>-16.1821</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2075</v>
+        <v>3.096400000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.0524</v>
+        <v>-8.1005</v>
       </c>
       <c r="H27" t="n">
-        <v>-4.3208</v>
+        <v>-4.376899999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.7316</v>
+        <v>-3.7236</v>
       </c>
       <c r="J27" t="n">
-        <v>-5.4109</v>
+        <v>-5.6787</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.8654</v>
+        <v>-2.071000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-3.5458</v>
+        <v>-3.6075</v>
       </c>
       <c r="M27" t="n">
-        <v>-2.6415</v>
+        <v>-2.4218</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.4553</v>
+        <v>-2.3058</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.1859999999999999</v>
+        <v>-0.1159</v>
       </c>
       <c r="P27" t="n">
-        <v>5.670799999999999</v>
+        <v>5.6907</v>
       </c>
       <c r="Q27" t="n">
-        <v>-19.2809</v>
+        <v>-19.3487</v>
       </c>
       <c r="R27" t="n">
-        <v>24.9515</v>
+        <v>25.0394</v>
       </c>
       <c r="S27" t="n">
-        <v>-3.916700000000001</v>
+        <v>-2.347</v>
       </c>
       <c r="T27" t="n">
-        <v>3.977200000000001</v>
+        <v>4.0139</v>
       </c>
       <c r="U27" t="n">
-        <v>-7.894</v>
+        <v>-6.3609</v>
       </c>
       <c r="V27" t="n">
-        <v>-8.355599999999999</v>
+        <v>-8.3286</v>
       </c>
       <c r="W27" t="n">
-        <v>4.8529</v>
+        <v>4.8312</v>
       </c>
       <c r="X27" t="n">
-        <v>-13.2085</v>
+        <v>-13.1599</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104494_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104494_W4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-4.8312</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104494_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-13.1599</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
